--- a/docs/Roadmap.xlsx
+++ b/docs/Roadmap.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1 done, 1 next, 17 planned</t>
+          <t>2 done, 1 next, 16 planned</t>
         </is>
       </c>
     </row>
@@ -953,9 +953,9 @@
           <t>Mac</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Next</t>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -990,9 +990,9 @@
           <t>Mac</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
         </is>
       </c>
     </row>

--- a/docs/Roadmap.xlsx
+++ b/docs/Roadmap.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2 done, 1 next, 16 planned</t>
+          <t>3 done, 1 next, 15 planned</t>
         </is>
       </c>
     </row>
@@ -990,9 +990,9 @@
           <t>Mac</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Next</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1027,9 +1027,9 @@
           <t>Mac</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Next</t>
         </is>
       </c>
     </row>
